--- a/weights.xlsx
+++ b/weights.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E146"/>
+  <dimension ref="A1:E160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" min="1" max="1"/>
@@ -2711,6 +2711,216 @@
       <c r="C146" t="inlineStr">
         <is>
           <t>Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>212.2</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>210.6</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>212.8</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>187</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>196</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>210.9</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>209.9</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>200.3</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>202.4</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>211.9</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>210.7</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Marat</t>
         </is>
       </c>
     </row>

--- a/weights.xlsx
+++ b/weights.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E160"/>
+  <dimension ref="A1:E172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" min="1" max="1"/>
@@ -2919,6 +2919,186 @@
         <v>182.4</v>
       </c>
       <c r="C160" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>213</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>183</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>209.8</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>209.4</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>184</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>213.8</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>207.7</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>205.1</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="C172" t="inlineStr">
         <is>
           <t>Marat</t>
         </is>

--- a/weights.xlsx
+++ b/weights.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E172"/>
+  <dimension ref="A1:F202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" min="1" max="1"/>
@@ -434,6 +434,11 @@
           <t>Weight (lbs)</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
       <c r="D1" t="inlineStr">
         <is>
           <t>Body Fat %</t>
@@ -442,6 +447,11 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>Waist Size (in)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ID</t>
         </is>
       </c>
     </row>
@@ -457,6 +467,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -470,6 +483,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -483,6 +499,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -496,6 +515,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -509,6 +531,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -522,6 +547,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -535,6 +563,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F8" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -548,6 +579,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -561,6 +595,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F10" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -574,6 +611,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -587,6 +627,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F12" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -600,6 +643,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F13" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -613,6 +659,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F14" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -626,6 +675,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F15" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -639,6 +691,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F16" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -658,6 +713,9 @@
       <c r="E17" t="n">
         <v>38</v>
       </c>
+      <c r="F17" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -677,6 +735,9 @@
       <c r="E18" t="n">
         <v>39</v>
       </c>
+      <c r="F18" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -696,6 +757,9 @@
       <c r="E19" t="n">
         <v>38.5</v>
       </c>
+      <c r="F19" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -715,6 +779,9 @@
       <c r="E20" t="n">
         <v>38.75</v>
       </c>
+      <c r="F20" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -734,6 +801,9 @@
       <c r="E21" t="n">
         <v>39</v>
       </c>
+      <c r="F21" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -753,6 +823,9 @@
       <c r="E22" t="n">
         <v>39.5</v>
       </c>
+      <c r="F22" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -772,6 +845,9 @@
       <c r="E23" t="n">
         <v>40.5</v>
       </c>
+      <c r="F23" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -791,6 +867,9 @@
       <c r="E24" t="n">
         <v>41</v>
       </c>
+      <c r="F24" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -810,6 +889,9 @@
       <c r="E25" t="n">
         <v>40</v>
       </c>
+      <c r="F25" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -829,6 +911,9 @@
       <c r="E26" t="n">
         <v>40.5</v>
       </c>
+      <c r="F26" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -848,6 +933,9 @@
       <c r="E27" t="n">
         <v>40.5</v>
       </c>
+      <c r="F27" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -867,6 +955,9 @@
       <c r="E28" t="n">
         <v>40.25</v>
       </c>
+      <c r="F28" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -886,6 +977,9 @@
       <c r="E29" t="n">
         <v>40.5</v>
       </c>
+      <c r="F29" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -905,6 +999,9 @@
       <c r="E30" t="n">
         <v>40</v>
       </c>
+      <c r="F30" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -924,6 +1021,9 @@
       <c r="E31" t="n">
         <v>40.25</v>
       </c>
+      <c r="F31" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -943,6 +1043,9 @@
       <c r="E32" t="n">
         <v>39.25</v>
       </c>
+      <c r="F32" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -962,6 +1065,9 @@
       <c r="E33" t="n">
         <v>40.25</v>
       </c>
+      <c r="F33" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -981,6 +1087,9 @@
       <c r="E34" t="n">
         <v>40.75</v>
       </c>
+      <c r="F34" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -1000,6 +1109,9 @@
       <c r="E35" t="n">
         <v>40.5</v>
       </c>
+      <c r="F35" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -1019,6 +1131,9 @@
       <c r="E36" t="n">
         <v>40.25</v>
       </c>
+      <c r="F36" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -1032,6 +1147,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F37" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -1045,6 +1163,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F38" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -1058,6 +1179,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F39" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -1071,6 +1195,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F40" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -1084,6 +1211,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F41" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -1103,6 +1233,9 @@
       <c r="E42" t="n">
         <v>37</v>
       </c>
+      <c r="F42" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -1116,6 +1249,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F43" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -1129,6 +1265,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F44" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -1142,6 +1281,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F45" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -1155,6 +1297,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F46" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -1168,6 +1313,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F47" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -1181,6 +1329,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F48" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -1194,6 +1345,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F49" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -1207,6 +1361,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F50" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -1220,6 +1377,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F51" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -1233,6 +1393,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F52" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -1246,6 +1409,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F53" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -1259,6 +1425,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F54" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -1272,6 +1441,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F55" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -1285,6 +1457,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F56" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -1298,6 +1473,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F57" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -1311,6 +1489,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F58" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -1324,6 +1505,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F59" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -1337,6 +1521,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F60" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -1350,6 +1537,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F61" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -1363,6 +1553,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F62" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -1376,6 +1569,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F63" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -1389,6 +1585,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F64" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -1402,6 +1601,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F65" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -1415,6 +1617,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F66" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -1428,6 +1633,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F67" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -1441,6 +1649,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F68" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -1454,6 +1665,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F69" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -1467,6 +1681,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F70" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -1480,6 +1697,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F71" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -1493,6 +1713,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F72" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -1506,6 +1729,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F73" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -1519,6 +1745,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F74" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -1532,6 +1761,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F75" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -1545,6 +1777,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F76" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -1558,6 +1793,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F77" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -1571,6 +1809,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F78" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -1584,6 +1825,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F79" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -1597,6 +1841,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F80" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -1610,6 +1857,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F81" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -1623,6 +1873,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F82" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -1636,6 +1889,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F83" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1651,6 +1907,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F84" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1666,6 +1925,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F85" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1687,6 +1949,9 @@
       <c r="E86" t="n">
         <v>38.5</v>
       </c>
+      <c r="F86" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1702,6 +1967,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F87" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1723,6 +1991,9 @@
       <c r="E88" t="n">
         <v>38</v>
       </c>
+      <c r="F88" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1738,6 +2009,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F89" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1759,6 +2033,9 @@
       <c r="E90" t="n">
         <v>38.5</v>
       </c>
+      <c r="F90" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1774,6 +2051,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F91" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1795,6 +2075,9 @@
       <c r="E92" t="n">
         <v>37.3</v>
       </c>
+      <c r="F92" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1810,6 +2093,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F93" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1831,6 +2117,9 @@
       <c r="E94" t="n">
         <v>38</v>
       </c>
+      <c r="F94" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1846,6 +2135,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F95" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1867,6 +2159,9 @@
       <c r="E96" t="n">
         <v>38.5</v>
       </c>
+      <c r="F96" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1882,6 +2177,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F97" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1903,6 +2201,9 @@
       <c r="E98" t="n">
         <v>39</v>
       </c>
+      <c r="F98" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1918,6 +2219,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F99" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1933,6 +2237,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F100" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1954,6 +2261,9 @@
       <c r="E101" t="n">
         <v>39</v>
       </c>
+      <c r="F101" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1969,6 +2279,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F102" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1990,6 +2303,9 @@
       <c r="E103" t="n">
         <v>39</v>
       </c>
+      <c r="F103" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2005,6 +2321,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F104" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2026,6 +2345,9 @@
       <c r="E105" t="n">
         <v>40</v>
       </c>
+      <c r="F105" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2041,6 +2363,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F106" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2062,6 +2387,9 @@
       <c r="E107" t="n">
         <v>39.5</v>
       </c>
+      <c r="F107" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2077,6 +2405,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F108" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2092,6 +2423,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F109" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2113,6 +2447,9 @@
       <c r="E110" t="n">
         <v>40</v>
       </c>
+      <c r="F110" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2134,6 +2471,9 @@
       <c r="E111" t="n">
         <v>39.75</v>
       </c>
+      <c r="F111" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2149,6 +2489,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F112" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2170,6 +2513,9 @@
       <c r="E113" t="n">
         <v>39.75</v>
       </c>
+      <c r="F113" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2185,6 +2531,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F114" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2200,6 +2549,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F115" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2215,6 +2567,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F116" t="n">
+        <v>115</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2230,6 +2585,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F117" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2245,6 +2603,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F118" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2266,6 +2627,9 @@
       <c r="E119" t="n">
         <v>40.5</v>
       </c>
+      <c r="F119" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2281,6 +2645,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F120" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2296,6 +2663,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F121" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2311,6 +2681,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F122" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2326,6 +2699,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F123" t="n">
+        <v>122</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2341,6 +2717,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F124" t="n">
+        <v>123</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2362,6 +2741,9 @@
       <c r="E125" t="n">
         <v>39.75</v>
       </c>
+      <c r="F125" t="n">
+        <v>124</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2377,6 +2759,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F126" t="n">
+        <v>125</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2398,6 +2783,9 @@
       <c r="E127" t="n">
         <v>39</v>
       </c>
+      <c r="F127" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2413,6 +2801,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F128" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2434,6 +2825,9 @@
       <c r="E129" t="n">
         <v>38.5</v>
       </c>
+      <c r="F129" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2449,6 +2843,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F130" t="n">
+        <v>129</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2470,6 +2867,9 @@
       <c r="E131" t="n">
         <v>38</v>
       </c>
+      <c r="F131" t="n">
+        <v>130</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2485,6 +2885,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F132" t="n">
+        <v>131</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2506,6 +2909,9 @@
       <c r="E133" t="n">
         <v>38</v>
       </c>
+      <c r="F133" t="n">
+        <v>132</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2521,6 +2927,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F134" t="n">
+        <v>133</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2542,6 +2951,9 @@
       <c r="E135" t="n">
         <v>40</v>
       </c>
+      <c r="F135" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2557,6 +2969,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F136" t="n">
+        <v>135</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2578,6 +2993,9 @@
       <c r="E137" t="n">
         <v>40</v>
       </c>
+      <c r="F137" t="n">
+        <v>136</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2593,6 +3011,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F138" t="n">
+        <v>137</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2608,6 +3029,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F139" t="n">
+        <v>138</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2623,6 +3047,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F140" t="n">
+        <v>139</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2638,6 +3065,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F141" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2653,6 +3083,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F142" t="n">
+        <v>141</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2668,6 +3101,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F143" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2683,6 +3119,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F144" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2698,6 +3137,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F145" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2713,6 +3155,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F146" t="n">
+        <v>145</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2728,6 +3173,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F147" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2743,6 +3191,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F148" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2758,6 +3209,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F149" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2773,6 +3227,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F150" t="n">
+        <v>149</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2788,6 +3245,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F151" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2803,6 +3263,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F152" t="n">
+        <v>151</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2818,6 +3281,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F153" t="n">
+        <v>152</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2833,6 +3299,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F154" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2848,6 +3317,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F155" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2863,6 +3335,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F156" t="n">
+        <v>155</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2878,6 +3353,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F157" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2893,6 +3371,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F158" t="n">
+        <v>157</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2908,6 +3389,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F159" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2923,6 +3407,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F160" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2938,6 +3425,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F161" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2953,6 +3443,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F162" t="n">
+        <v>161</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2968,6 +3461,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F163" t="n">
+        <v>162</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2983,6 +3479,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F164" t="n">
+        <v>163</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2998,6 +3497,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F165" t="n">
+        <v>164</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3013,6 +3515,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F166" t="n">
+        <v>165</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3028,6 +3533,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F167" t="n">
+        <v>166</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3043,6 +3551,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F168" t="n">
+        <v>167</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3058,6 +3569,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F169" t="n">
+        <v>168</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3073,6 +3587,9 @@
           <t>Marat</t>
         </is>
       </c>
+      <c r="F170" t="n">
+        <v>169</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3088,6 +3605,9 @@
           <t>Michael</t>
         </is>
       </c>
+      <c r="F171" t="n">
+        <v>170</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3102,6 +3622,567 @@
         <is>
           <t>Marat</t>
         </is>
+      </c>
+      <c r="F172" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>203.1</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>180.4</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>183</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>208</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>206</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>208.7</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>190</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>212</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>212.4</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>210.4</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>211.3</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>209.1</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>187</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>209</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>207.1</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>206.5</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E198" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="F198" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>206.1</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E199" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="F199" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>186.2</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Marat</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>204.2</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="E202" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="F202" t="n">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -3115,7 +4196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3134,6 +4215,11 @@
           <t>Goal Weight (lbs)</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Height (in)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
